--- a/out/LSTM_Base_repeat_2_000006.xlsx
+++ b/out/LSTM_Base_repeat_2_000006.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.295895168639794</v>
+        <v>8.62785843586423</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.295895168639794</v>
+        <v>8.62785843586423</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.295895168639794</v>
+        <v>9.227858435864231</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.295895168639794</v>
+        <v>0.0804624974787484</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.295895168639794</v>
+        <v>0.0804624974787484</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.668078547550069</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.268078547550068</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>2.268078547550068</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.6958951686397941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.6958951686397941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.668078547550069</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>2.268078547550068</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.6958951686397941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.668078547550069</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.268078547550068</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.268078547550068</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.268078547550068</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.268078547550068</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.668078547550069</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.668078547550069</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.268078547550068</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.268078547550068</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.268078547550068</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>2.268078547550068</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>2.268078547550068</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.668078547550069</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.668078547550069</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.268078547550068</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.268078547550068</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.268078547550068</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.268078547550068</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.268078547550068</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.268078547550068</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.268078547550068</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.668078547550069</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0002914773716836935</v>
+        <v>-4.036279517633375e-05</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3751538718892948</v>
+        <v>0.05195006150234709</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.668078547550069</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.7510181372481496</v>
+        <v>0.1039984375104874</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.08663854626395577</v>
+        <v>-0.01199740451623276</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.668078547550069</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.2882238482536553</v>
+        <v>0.03991229419093812</v>
       </c>
     </row>
     <row r="47">
@@ -38302,17 +38302,17 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.2882238482536553</v>
+        <v>0.03991229419093812</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2882238482536553</v>
+        <v>0.03985383340237522</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0</v>
+        <v>0.1796040234711458</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.2882064137879712</v>
+        <v>0.399419839118378</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>-0.01626740924847012</v>
+        <v>0.0343652061752737</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.668078547550069</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.2719390045395012</v>
+        <v>0.2882839304288852</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0</v>
+        <v>0.06019413528315388</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.668078547550069</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.271672890810688</v>
+        <v>0.3743237162471069</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0</v>
+        <v>0.03296449898149532</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>2.268078547550068</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.3124317209537723</v>
+        <v>0.380006695219364</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>-0.0534802776285672</v>
+        <v>0.01361462133948809</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.6958951686397941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.2181510556091785</v>
+        <v>0.3742372758438992</v>
       </c>
     </row>
     <row r="54">
@@ -43863,21 +43863,21 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0</v>
+        <v>0.0169626498609169</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>2.268078547550068</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.2178476549505594</v>
+        <v>0.3945508274791141</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.05540763759401857</v>
+        <v>0.01021204948025571</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.268078547550068</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.3292019511143801</v>
+        <v>0.3980026232258966</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.1134238212184046</v>
+        <v>0.007763531111272499</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.268078547550068</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.5005020342360181</v>
+        <v>0.4033129624394879</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.04226470244442003</v>
+        <v>0.003431049445745289</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.6958951686397941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.4713865655575974</v>
+        <v>0.4024060506027483</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.05363856959297019</v>
+        <v>0.002721510970127304</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.5363600498912937</v>
+        <v>0.4044170334317791</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.02645810459236552</v>
+        <v>0.001345799342184725</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.668078547550069</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.5355683503417836</v>
+        <v>0.4043879042595944</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.01678162054813013</v>
+        <v>0.0007804842013199761</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.668078547550069</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5426431857721947</v>
+        <v>0.4046027680698263</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.008389755702384696</v>
+        <v>0.0003877421006599881</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.6958951686397941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.5426224040589163</v>
+        <v>0.4045972790793989</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.004116158960671259</v>
+        <v>0.0001904760750419558</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.5424588789514992</v>
+        <v>0.4045873307989093</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.002559791506638035</v>
+        <v>0.000108480194448693</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5434594730311448</v>
+        <v>0.4046137122843436</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0006759762917001497</v>
+        <v>3.294349193752244e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5422463003254668</v>
+        <v>0.4045710261632488</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0003386227180159716</v>
+        <v>1.296632917816834e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5422480734103222</v>
+        <v>0.4045662388022761</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.0001940664366738808</v>
+        <v>4.784784520434025e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5422974327427451</v>
+        <v>0.4045630323505828</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>8.936415188306374e-05</v>
+        <v>-2.596391060734771e-07</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5422818038127727</v>
+        <v>0.4045576458664252</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>6.050876609618538e-05</v>
+        <v>-2.090799254370459e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5423139177447382</v>
+        <v>0.4045542612479743</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>2.211540146204546e-05</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5422972393267628</v>
+        <v>0.4045485938177006</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>1.277591828026595e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5422990558353786</v>
+        <v>0.4045489743527584</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>3.812596322305575e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5422960949076722</v>
+        <v>0.4045492026737931</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>-4.140284059584509e-07</v>
+        <v>0</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5422915365065459</v>
+        <v>0.404549292618443</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>-3.563918267525618e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5422839596731237</v>
+        <v>0.4045484346848582</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>-3.335871218089884e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5422794130085397</v>
+        <v>0.4045486630058929</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5422786173443279</v>
+        <v>0.4045478673416811</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.542278679613701</v>
+        <v>0.4045479296110542</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5422787072889779</v>
+        <v>0.4045479572863311</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5422788595030013</v>
+        <v>0.4045481095003544</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5422785135620395</v>
+        <v>0.4045477635593926</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5422785896690511</v>
+        <v>0.4045478396664043</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5422787557207127</v>
+        <v>0.4045480057180659</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5422791154993127</v>
+        <v>0.404548365496666</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.268078547550068</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5422791362557705</v>
+        <v>0.4045483862531236</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.268078547550068</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5422792400380589</v>
+        <v>0.4045484900354122</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.6958951686397941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5422794683590937</v>
+        <v>0.4045487183564468</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.6958951686397941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5422793438203475</v>
+        <v>0.4045485938177006</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5422793714956243</v>
+        <v>0.4045486214929775</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5422794268461782</v>
+        <v>0.4045486768435314</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5422796897613089</v>
+        <v>0.4045489397586621</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5422796067354781</v>
+        <v>0.4045488567328314</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5422793991709014</v>
+        <v>0.4045486491682546</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.5422794130085397</v>
+        <v>0.4045486630058929</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5422795513849245</v>
+        <v>0.4045488013822776</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5422792677133358</v>
+        <v>0.404548517710689</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5422790947428551</v>
+        <v>0.4045483447402082</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5422789909605665</v>
+        <v>0.4045482409579197</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5422791362557705</v>
+        <v>0.4045483862531236</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.5422793784144437</v>
+        <v>0.4045486284117969</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5422792054439627</v>
+        <v>0.4045484554413159</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.5422789079347358</v>
+        <v>0.4045481579320889</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5422788940970972</v>
+        <v>0.4045481440944504</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.542278527399678</v>
+        <v>0.4045477773970312</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.542278527399678</v>
+        <v>0.4045477773970312</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5422784651303049</v>
+        <v>0.4045477151276581</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5422783613480164</v>
+        <v>0.4045476113453696</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.5422781883775357</v>
+        <v>0.4045474383748888</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5422782368092702</v>
+        <v>0.4045474868066234</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5422778770306702</v>
+        <v>0.4045471270280234</v>
       </c>
     </row>
     <row r="109">
@@ -87588,21 +87588,21 @@
         <v>0</v>
       </c>
       <c r="IY109" t="n">
-        <v>-4.911469014191316e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA109" t="n">
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5422728341040904</v>
+        <v>0.404547085515108</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA110" t="n">
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5422728341040904</v>
+        <v>0.4045471408656617</v>
       </c>
     </row>
     <row r="111">
@@ -89182,17 +89182,17 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA111" t="n">
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5422728341040904</v>
+        <v>0.4045471962162156</v>
       </c>
     </row>
     <row r="112">
@@ -89977,17 +89977,17 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA112" t="n">
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5422728341040904</v>
+        <v>0.404547237729131</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.5422728341040904</v>
+        <v>0.4045469678951809</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA114" t="n">
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5422728341040904</v>
+        <v>0.4045470232457349</v>
       </c>
     </row>
     <row r="115">
@@ -92362,17 +92362,17 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA115" t="n">
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5422728341040904</v>
+        <v>0.4045471685409388</v>
       </c>
     </row>
     <row r="116">
@@ -93157,17 +93157,17 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA116" t="n">
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5422728341040904</v>
+        <v>0.4045471339468425</v>
       </c>
     </row>
     <row r="117">
@@ -93952,17 +93952,17 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA117" t="n">
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5422728341040904</v>
+        <v>0.404547120109204</v>
       </c>
     </row>
     <row r="118">
@@ -94747,17 +94747,17 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.268078547550068</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5417826718933997</v>
+        <v>0.4045472100538541</v>
       </c>
     </row>
     <row r="119">
@@ -95538,7 +95538,7 @@
         <v>0</v>
       </c>
       <c r="IY119" t="n">
-        <v>0.11884753638359</v>
+        <v>0</v>
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.268078547550068</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.7803929488988905</v>
+        <v>0.4045475283195388</v>
       </c>
     </row>
     <row r="120">
@@ -96333,7 +96333,7 @@
         <v>0</v>
       </c>
       <c r="IY120" t="n">
-        <v>0.025628703181981</v>
+        <v>0</v>
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>2.268078547550068</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.7122942898550357</v>
+        <v>0.4045473484302387</v>
       </c>
     </row>
     <row r="121">
@@ -97128,7 +97128,7 @@
         <v>0</v>
       </c>
       <c r="IY121" t="n">
-        <v>0.01671371155747239</v>
+        <v>0</v>
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.6958951686397941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.7198957089185354</v>
+        <v>0.4045473899431541</v>
       </c>
     </row>
     <row r="122">
@@ -97923,21 +97923,21 @@
         <v>0</v>
       </c>
       <c r="IY122" t="n">
-        <v>-8.690608206870434e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA122" t="n">
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.6958951686397941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.7023017063217655</v>
+        <v>0.4045472031350348</v>
       </c>
     </row>
     <row r="123">
@@ -98718,21 +98718,21 @@
         <v>0</v>
       </c>
       <c r="IY123" t="n">
-        <v>0.005083285605184323</v>
+        <v>0</v>
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA123" t="n">
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.7079690025395583</v>
+        <v>0.4045472723232272</v>
       </c>
     </row>
     <row r="124">
@@ -99517,17 +99517,17 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA124" t="n">
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.7079690025395583</v>
+        <v>0.4045470716774694</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.7079690025395583</v>
+        <v>0.4045471131903848</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>0</v>
+        <v>-3.873712549958921e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell (Force)</t>
         </is>
       </c>
       <c r="JA126" t="n">
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.7079690025395583</v>
+        <v>0.4045471408656617</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM_Base_repeat_2_000006.xlsx
+++ b/out/LSTM_Base_repeat_2_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.04541983765246159</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.668078547550069</v>
+        <v>0.6320598689052213</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.268078547550068</v>
+        <v>1.509539575462904</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>2.268078547550068</v>
+        <v>0.8320598689052213</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.6958951686397941</v>
+        <v>0.1545801623475385</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.6958951686397941</v>
+        <v>0.1545801623475385</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.668078547550069</v>
+        <v>0.8320598689052213</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>2.268078547550068</v>
+        <v>0.8320598689052214</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.6958951686397941</v>
+        <v>0.1545801623475385</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.04541983765246159</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.668078547550069</v>
+        <v>0.6320598689052213</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.268078547550068</v>
+        <v>1.509539575462904</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.268078547550068</v>
+        <v>1.509539575462904</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.268078547550068</v>
+        <v>1.509539575462904</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.268078547550068</v>
+        <v>0.8320598689052213</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.04541983765246159</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.04541983765246159</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.668078547550069</v>
+        <v>0.6320598689052213</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.668078547550069</v>
+        <v>1.309539575462904</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.268078547550068</v>
+        <v>1.509539575462904</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.268078547550068</v>
+        <v>1.509539575462904</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.268078547550068</v>
+        <v>1.509539575462904</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>2.268078547550068</v>
+        <v>1.509539575462904</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>2.268078547550068</v>
+        <v>0.8320598689052213</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.04541983765246159</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.04541983765246159</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.668078547550069</v>
+        <v>0.6320598689052213</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.668078547550069</v>
+        <v>1.309539575462904</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.268078547550068</v>
+        <v>1.509539575462904</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.268078547550068</v>
+        <v>1.509539575462904</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.268078547550068</v>
+        <v>1.509539575462904</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.268078547550068</v>
+        <v>1.509539575462904</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.268078547550068</v>
+        <v>1.509539575462904</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.268078547550068</v>
+        <v>1.509539575462904</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.268078547550068</v>
+        <v>1.509539575462904</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.668078547550069</v>
+        <v>1.509539575462904</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0002914773716836935</v>
+        <v>-0.0002732788100215839</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3751538718892948</v>
+        <v>0.3517311158925713</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.668078547550069</v>
+        <v>1.309539575462904</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.7510181372481496</v>
+        <v>0.7041278762489032</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.08663854626395577</v>
+        <v>-0.08122917194464671</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.668078547550069</v>
+        <v>0.6320598689052214</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.2882238482536553</v>
+        <v>0.2702286651379031</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.04541983765246159</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.2882238482536553</v>
+        <v>0.2702286651379031</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2882238482536553</v>
+        <v>0.2701790256864033</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0</v>
+        <v>0.1525031304977452</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.04541983765246159</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.2882064137879712</v>
+        <v>0.5754889560589553</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>-0.01626740924847012</v>
+        <v>0.02917975566828905</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.668078547550069</v>
+        <v>0.6320598689052213</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.2719390045395012</v>
+        <v>0.4811227884242087</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0</v>
+        <v>0.05111110940528694</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.668078547550069</v>
+        <v>1.309539575462904</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.271672890810688</v>
+        <v>0.5541795552583244</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0</v>
+        <v>0.02799006521206575</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>2.268078547550068</v>
+        <v>0.8320598689052213</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.3124317209537723</v>
+        <v>0.5590049985503347</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>-0.0534802776285672</v>
+        <v>0.01155970999125422</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.6958951686397941</v>
+        <v>0.8320598689052213</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.2181510556091785</v>
+        <v>0.5541055225502262</v>
       </c>
     </row>
     <row r="54">
@@ -43863,21 +43863,21 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0</v>
+        <v>0.01440343152687631</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>2.268078547550068</v>
+        <v>0.8320598689052213</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.2178476549505594</v>
+        <v>0.5713538341691822</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.05540763759401857</v>
+        <v>0.008670098564130611</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.268078547550068</v>
+        <v>1.509539575462904</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.3292019511143801</v>
+        <v>0.574283962677982</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.1134238212184046</v>
+        <v>0.006590346371295408</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.268078547550068</v>
+        <v>0.8320598689052213</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.5005020342360181</v>
+        <v>0.5787922080211393</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.04226470244442003</v>
+        <v>0.002912940232372041</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.6958951686397941</v>
+        <v>0.1545801623475385</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.4713865655575974</v>
+        <v>0.5780212921412808</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.05363856959297019</v>
+        <v>0.002310390444566943</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.04541983765246159</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.5363600498912937</v>
+        <v>0.5797282923605687</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.02645810459236552</v>
+        <v>0.001143179440857017</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.668078547550069</v>
+        <v>0.6320598689052213</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.5355683503417836</v>
+        <v>0.5797028002072007</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.01678162054813013</v>
+        <v>0.0006612069707491649</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.668078547550069</v>
+        <v>0.6320598689052214</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5426431857721947</v>
+        <v>0.5798843392781891</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.008389755702384696</v>
+        <v>0.0003295580857473972</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.6958951686397941</v>
+        <v>-0.04541983765246159</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.5426224040589163</v>
+        <v>0.5798789227307879</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.004116158960671259</v>
+        <v>0.000158854945255757</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.5424588789514992</v>
+        <v>0.5798697403133405</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.002559791506638035</v>
+        <v>9.179193055917936e-05</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5434594730311448</v>
+        <v>0.579891506874446</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0006759762917001497</v>
+        <v>2.624758159560671e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5422463003254668</v>
+        <v>0.5798543642342321</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0003386227180159716</v>
+        <v>1.07205380308973e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5422480734103222</v>
+        <v>0.5798495520230857</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.0001940664366738808</v>
+        <v>4.784784520434025e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5422974327427451</v>
+        <v>0.5798461449256346</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>8.936415188306374e-05</v>
+        <v>-2.596391060734771e-07</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5422818038127727</v>
+        <v>0.5798408345484887</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>6.050876609618538e-05</v>
+        <v>-2.090799254370459e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5423139177447382</v>
+        <v>0.5798369102621377</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>2.211540146204546e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5422972393267628</v>
+        <v>0.5798365781588145</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>1.277591828026595e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5422990558353786</v>
+        <v>0.5798369586938722</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>3.812596322305575e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5422960949076722</v>
+        <v>0.5798371870149069</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>-4.140284059584509e-07</v>
+        <v>0</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5422915365065459</v>
+        <v>0.5798372769595569</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>-3.563918267525618e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5422839596731237</v>
+        <v>0.579836419025972</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>-3.335871218089884e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5422794130085397</v>
+        <v>0.5798366473470067</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5422786173443279</v>
+        <v>0.5798358516827949</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.542278679613701</v>
+        <v>0.579835913952168</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5422787072889779</v>
+        <v>0.5798359416274449</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5422788595030013</v>
+        <v>0.5798360938414682</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5422785135620395</v>
+        <v>0.5798357479005065</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5422785896690511</v>
+        <v>0.5798358240075181</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5422787557207127</v>
+        <v>0.5798359900591797</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.295895168639794</v>
+        <v>0.1545801623475385</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5422791154993127</v>
+        <v>0.5798363498377798</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.268078547550068</v>
+        <v>0.8320598689052213</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5422791362557705</v>
+        <v>0.5798363705942374</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.268078547550068</v>
+        <v>0.8320598689052214</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5422792400380589</v>
+        <v>0.579836474376526</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.6958951686397941</v>
+        <v>0.1545801623475385</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5422794683590937</v>
+        <v>0.5798367026975606</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.6958951686397941</v>
+        <v>-0.5228995442101445</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5422793438203475</v>
+        <v>0.5798365781588145</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5422793714956243</v>
+        <v>0.5798366058340914</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5422794268461782</v>
+        <v>0.5798366611846453</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5422796897613089</v>
+        <v>0.5798369240997759</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5422796067354781</v>
+        <v>0.5798368410739452</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5422793991709014</v>
+        <v>0.5798366335093684</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.5422794130085397</v>
+        <v>0.5798366473470067</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5422795513849245</v>
+        <v>0.5798367857233915</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5422792677133358</v>
+        <v>0.5798365020518028</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5422790947428551</v>
+        <v>0.5798363290813221</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5422789909605665</v>
+        <v>0.5798362252990336</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5422791362557705</v>
+        <v>0.5798363705942374</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.5422793784144437</v>
+        <v>0.5798366127529107</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5422792054439627</v>
+        <v>0.5798364397824297</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.5422789079347358</v>
+        <v>0.5798361422732028</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5422788940970972</v>
+        <v>0.5798361284355642</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.542278527399678</v>
+        <v>0.579835761738145</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.542278527399678</v>
+        <v>0.579835761738145</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5422784651303049</v>
+        <v>0.5798356994687719</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5422783613480164</v>
+        <v>0.5798355956864835</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.5422781883775357</v>
+        <v>0.5798354227160026</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5422782368092702</v>
+        <v>0.5798354711477373</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5422778770306702</v>
+        <v>0.5798351113691372</v>
       </c>
     </row>
     <row r="109">
@@ -87588,21 +87588,21 @@
         <v>0</v>
       </c>
       <c r="IY109" t="n">
-        <v>-4.911469014191316e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA109" t="n">
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5422728341040904</v>
+        <v>0.5798350698562218</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA110" t="n">
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5422728341040904</v>
+        <v>0.5798351252067755</v>
       </c>
     </row>
     <row r="111">
@@ -89182,17 +89182,17 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA111" t="n">
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5422728341040904</v>
+        <v>0.5798351805573294</v>
       </c>
     </row>
     <row r="112">
@@ -89977,17 +89977,17 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA112" t="n">
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5422728341040904</v>
+        <v>0.5798352220702448</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.5422728341040904</v>
+        <v>0.5798349522362948</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA114" t="n">
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5422728341040904</v>
+        <v>0.5798350075868487</v>
       </c>
     </row>
     <row r="115">
@@ -92362,17 +92362,17 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA115" t="n">
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5422728341040904</v>
+        <v>0.5798351528820526</v>
       </c>
     </row>
     <row r="116">
@@ -93157,17 +93157,17 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA116" t="n">
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5422728341040904</v>
+        <v>0.5798351182879563</v>
       </c>
     </row>
     <row r="117">
@@ -93952,17 +93952,17 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA117" t="n">
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.295895168639794</v>
+        <v>0.1545801623475385</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5422728341040904</v>
+        <v>0.5798351044503178</v>
       </c>
     </row>
     <row r="118">
@@ -94747,17 +94747,17 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA118" t="n">
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.268078547550068</v>
+        <v>0.8320598689052213</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5417826718933997</v>
+        <v>0.579835194394968</v>
       </c>
     </row>
     <row r="119">
@@ -95538,7 +95538,7 @@
         <v>0</v>
       </c>
       <c r="IY119" t="n">
-        <v>0.11884753638359</v>
+        <v>0</v>
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.268078547550068</v>
+        <v>1.509539575462904</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.7803929488988905</v>
+        <v>0.5798355126606526</v>
       </c>
     </row>
     <row r="120">
@@ -96333,7 +96333,7 @@
         <v>0</v>
       </c>
       <c r="IY120" t="n">
-        <v>0.025628703181981</v>
+        <v>0</v>
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
@@ -96344,10 +96344,10 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>2.268078547550068</v>
+        <v>0.8320598689052213</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.7122942898550357</v>
+        <v>0.5798353327713525</v>
       </c>
     </row>
     <row r="121">
@@ -97128,7 +97128,7 @@
         <v>0</v>
       </c>
       <c r="IY121" t="n">
-        <v>0.01671371155747239</v>
+        <v>0</v>
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.6958951686397941</v>
+        <v>0.1545801623475385</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.7198957089185354</v>
+        <v>0.5798353742842679</v>
       </c>
     </row>
     <row r="122">
@@ -97923,21 +97923,21 @@
         <v>0</v>
       </c>
       <c r="IY122" t="n">
-        <v>-8.690608206870434e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA122" t="n">
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.6958951686397941</v>
+        <v>-0.5228995442101445</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.7023017063217655</v>
+        <v>0.5798351874761486</v>
       </c>
     </row>
     <row r="123">
@@ -98718,21 +98718,21 @@
         <v>0</v>
       </c>
       <c r="IY123" t="n">
-        <v>0.005083285605184323</v>
+        <v>0</v>
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA123" t="n">
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.7079690025395583</v>
+        <v>0.5798352566643411</v>
       </c>
     </row>
     <row r="124">
@@ -99517,17 +99517,17 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA124" t="n">
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.7079690025395583</v>
+        <v>0.5798350560185832</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.7079690025395583</v>
+        <v>0.5798350975314986</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>0</v>
+        <v>-3.873712549958921e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell (Force)</t>
         </is>
       </c>
       <c r="JA126" t="n">
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.7079690025395583</v>
+        <v>0.5798351252067755</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM_Base_repeat_2_000006.xlsx
+++ b/out/LSTM_Base_repeat_2_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.02168918401002884</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-1.28</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.01508630067110062</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9299999999999997</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.008542658761143684</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.003206852823495865</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.3</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.0018270593136549</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.0004364475607872009</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.0009299926459789276</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.04541983765246159</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.0006188265979290009</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.6320598689052213</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.001568809151649475</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.509539575462904</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.0003524422645568848</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.8320598689052213</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.0008932314813137054</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.1545801623475385</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.00144449807703495</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.1545801623475385</v>
+        <v>-0.16</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.0002923589199781418</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.8320598689052213</v>
+        <v>-0.3</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.0003585461527109146</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.8320598689052214</v>
+        <v>-0.16</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.0001778565347194672</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.1545801623475385</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.0006277784705162048</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.04541983765246159</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.0002602003514766693</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.6320598689052213</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.001626815646886826</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.509539575462904</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.003446595743298531</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.509539575462904</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.002536032348871231</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.509539575462904</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.0008201152086257935</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.8320598689052213</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.0007551666349172592</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.04541983765246159</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.00107947550714016</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.04541983765246159</v>
+        <v>-0.16</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.001205660402774811</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.6320598689052213</v>
+        <v>-0.16</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.0007914714515209198</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.309539575462904</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.003231227397918701</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.509539575462904</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.008311368525028229</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.509539575462904</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.005998164415359497</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.509539575462904</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.001807713881134987</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.509539575462904</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>9.532272815704346e-05</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.8320598689052213</v>
+        <v>-0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.001464175060391426</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.04541983765246159</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.002423947677016258</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.001626370474696159</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.04541983765246159</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.002525389194488525</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.6320598689052213</v>
+        <v>-0.16</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.002391835674643517</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.309539575462904</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.001402257010340691</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.509539575462904</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.001722473651170731</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.509539575462904</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.0004025492817163467</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.509539575462904</v>
+        <v>0.3</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.0001466330140829086</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.509539575462904</v>
+        <v>0.3</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.001171592622995377</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.509539575462904</v>
+        <v>-0.3</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.003682922571897507</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.509539575462904</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.006601627916097641</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.509539575462904</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.01128197833895683</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.509539575462904</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0002732788100215839</v>
+        <v>-0.0001826481971237809</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3517311158925713</v>
+        <v>0.2350824573080914</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.009805932641029358</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.309539575462904</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.7041278762489032</v>
+        <v>0.4706098037066381</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.08122917194464671</v>
+        <v>-0.05429020204081502</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.0004304219037294388</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.6320598689052214</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.2702286651379031</v>
+        <v>0.1806096070701526</v>
       </c>
     </row>
     <row r="47">
@@ -38302,17 +38302,17 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.002543136477470398</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.04541983765246159</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.2702286651379031</v>
+        <v>0.1806096070701526</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.001947673037648201</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2701790256864033</v>
+        <v>0.1805910395481882</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.1525031304977452</v>
+        <v>0.0570434430597642</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.00314398854970932</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.04541983765246159</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.5754889560589553</v>
+        <v>0.2947915124954945</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.02917975566828905</v>
+        <v>0.01091462008372666</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.0004352070391178131</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.6320598689052213</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.4811227884242087</v>
+        <v>0.259494065861634</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.05111110940528694</v>
+        <v>0.01911799219836324</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.001341680064797401</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.309539575462904</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.5541795552583244</v>
+        <v>0.2868207804374635</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.02799006521206575</v>
+        <v>0.01046855120193331</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.001117266714572906</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.8320598689052213</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.5590049985503347</v>
+        <v>0.2886245691298491</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.01155970999125422</v>
+        <v>0.004320592946778152</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.0009567812085151672</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.8320598689052213</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.5541055225502262</v>
+        <v>0.2867888174798759</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.01440343152687631</v>
+        <v>0.005384548135998066</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.004820751026272774</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.8320598689052213</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.5713538341691822</v>
+        <v>0.2932375076891319</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.008670098564130611</v>
+        <v>0.003239595567570506</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.003014791756868362</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.509539575462904</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.574283962677982</v>
+        <v>0.2943304081322081</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.006590346371295408</v>
+        <v>0.002461742186812474</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.007276196032762527</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.8320598689052213</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.5787922080211393</v>
+        <v>0.2960138039118054</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.002912940232372041</v>
+        <v>0.001086843649041172</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.002361869439482689</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.1545801623475385</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.5780212921412808</v>
+        <v>0.2957222112051263</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.002310390444566943</v>
+        <v>0.0008601186519460365</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.005669252946972847</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.04541983765246159</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.5797282923605687</v>
+        <v>0.2963578141729729</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.001143179440857017</v>
+        <v>0.0004252546052884681</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.00828118622303009</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.6320598689052213</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.5797028002072007</v>
+        <v>0.2963451351961116</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.0006612069707491649</v>
+        <v>0.0002451912641241405</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.01009503751993179</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.6320598689052214</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5798843392781891</v>
+        <v>0.2964100358686715</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0003295580857473972</v>
+        <v>0.0001200956320620703</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.002038272097706795</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.04541983765246159</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.5798789227307879</v>
+        <v>0.2964048801161652</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.000158854945255757</v>
+        <v>5.536761141001575e-05</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.008734038099646568</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.5798697403133405</v>
+        <v>0.2963983173766236</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>9.179193055917936e-05</v>
+        <v>3.17141805569301e-05</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.01140029262751341</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.579891506874446</v>
+        <v>0.2964034702101466</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>2.624758159560671e-05</v>
+        <v>6.159850569859539e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.01765849255025387</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5798543642342321</v>
+        <v>0.2963862790458063</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>1.07205380308973e-05</v>
+        <v>1.73737344181313e-06</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.0179809182882309</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5798495520230857</v>
+        <v>0.2963813535963271</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>4.784784520434025e-06</v>
+        <v>-2.553803869891494e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.01729864254593849</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5798461449256346</v>
+        <v>0.2963769524677221</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>-2.596391060734771e-07</v>
+        <v>-2.629819553036738e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.01172996871173382</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5798408345484887</v>
+        <v>0.2963717972791493</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>-2.090799254370459e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.007695281878113747</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5798369102621377</v>
+        <v>0.2963723369470495</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.006980838254094124</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5798365781588145</v>
+        <v>0.2963720048437263</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.004167685285210609</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5798369586938722</v>
+        <v>0.296372385378784</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.007261807098984718</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5798371870149069</v>
+        <v>0.2963726136998187</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.01051724702119827</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5798372769595569</v>
+        <v>0.2963727036444687</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.01324519142508507</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.579836419025972</v>
+        <v>0.2963718457108839</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.01315814908593893</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5798366473470067</v>
+        <v>0.2963720740319186</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.01308420300483704</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5798358516827949</v>
+        <v>0.2963712783677068</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.01447047013789415</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.579835913952168</v>
+        <v>0.2963713406370799</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.01241437904536724</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5798359416274449</v>
+        <v>0.2963713683123568</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.008397283032536507</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5798360938414682</v>
+        <v>0.2963715205263801</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.009102195501327515</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5798357479005065</v>
+        <v>0.2963711745854183</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.007764514535665512</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5798358240075181</v>
+        <v>0.29637125069243</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.008114542812108994</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.16</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5798359900591797</v>
+        <v>0.2963714167440916</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.003079731017351151</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.1545801623475385</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5798363498377798</v>
+        <v>0.2963717765226916</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>3.121234476566315e-05</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.8320598689052213</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5798363705942374</v>
+        <v>0.2963717972791493</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.001722147688269615</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.8320598689052214</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.579836474376526</v>
+        <v>0.2963719010614378</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.002555646002292633</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.1545801623475385</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5798367026975606</v>
+        <v>0.2963721293824725</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.006562391296029091</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.5228995442101445</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5798365781588145</v>
+        <v>0.2963720048437263</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.008792251348495483</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5798366058340914</v>
+        <v>0.2963720325190031</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.004647005349397659</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.3</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5798366611846453</v>
+        <v>0.2963720878695571</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.00558113306760788</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5798369240997759</v>
+        <v>0.2963723507846878</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.006647245958447456</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.16</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5798368410739452</v>
+        <v>0.296372267758857</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.007359510287642479</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.16</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5798366335093684</v>
+        <v>0.2963720601942803</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.007073132321238518</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.16</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.5798366473470067</v>
+        <v>0.2963720740319186</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.006913436576724052</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.3</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5798367857233915</v>
+        <v>0.2963722124083033</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.008082438260316849</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.16</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5798365020518028</v>
+        <v>0.2963719287367146</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.009049339219927788</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5798363290813221</v>
+        <v>0.2963717557662339</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.006018809974193573</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5798362252990336</v>
+        <v>0.2963716519839454</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.004528682678937912</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5798363705942374</v>
+        <v>0.2963717972791493</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.004449710249900818</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.5798366127529107</v>
+        <v>0.2963720394378225</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.005883043631911278</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5798364397824297</v>
+        <v>0.2963718664673415</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.007543619722127914</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.3</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.5798361422732028</v>
+        <v>0.2963715689581146</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.008209707215428352</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5798361284355642</v>
+        <v>0.2963715551204761</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.00882074236869812</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.579835761738145</v>
+        <v>0.2963711884230569</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.006555449217557907</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.579835761738145</v>
+        <v>0.2963711884230569</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.00493273138999939</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5798356994687719</v>
+        <v>0.2963711261536838</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.007180599495768547</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5798355956864835</v>
+        <v>0.2963710223713952</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.007708672434091568</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.5798354227160026</v>
+        <v>0.2963708494009145</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.007495537400245667</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5798354711477373</v>
+        <v>0.2963708978326491</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.00823507271707058</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5798351113691372</v>
+        <v>0.296370538054049</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.007732981815934181</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5798350698562218</v>
+        <v>0.2963704965411336</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.005145501345396042</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5798351252067755</v>
+        <v>0.2963705518916873</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.004838729277253151</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5798351805573294</v>
+        <v>0.2963706072422413</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.004641000181436539</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5798352220702448</v>
+        <v>0.2963706487551567</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.005022007972002029</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.5798349522362948</v>
+        <v>0.2963703789212066</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.003887906670570374</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5798350075868487</v>
+        <v>0.2963704342717605</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.003202950581908226</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5798351528820526</v>
+        <v>0.2963705795669644</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.00259963795542717</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5798351182879563</v>
+        <v>0.2963705449728682</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.002898111939430237</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.1545801623475385</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5798351044503178</v>
+        <v>0.2963705311352297</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.0007593818008899689</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.8320598689052213</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.579835194394968</v>
+        <v>0.2963706210798798</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.006374035030603409</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.509539575462904</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5798355126606526</v>
+        <v>0.2963709393455645</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.001135442405939102</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.8320598689052213</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5798353327713525</v>
+        <v>0.2963707594562643</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.003867495805025101</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.1545801623475385</v>
+        <v>-0.3</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5798353742842679</v>
+        <v>0.2963708009691797</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.005927866324782372</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.5228995442101445</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.5798351874761486</v>
+        <v>0.2963706141610604</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.007271099835634232</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5798352566643411</v>
+        <v>0.2963706833492529</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.006787661463022232</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5798350560185832</v>
+        <v>0.2963704827034951</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.006312165409326553</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.7199999999999995</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.5798350975314986</v>
+        <v>0.2963705242164105</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.004229243844747543</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.5799999999999995</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5798351252067755</v>
+        <v>0.2963705518916873</v>
       </c>
     </row>
   </sheetData>
